--- a/research/traditional_assets/database/data/new_zealand/new_zealand_chemical_specialty.xlsx
+++ b/research/traditional_assets/database/data/new_zealand/new_zealand_chemical_specialty.xlsx
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.626</v>
+        <v>-0.32825</v>
       </c>
       <c r="G2">
-        <v>-0.7740555951532431</v>
+        <v>-2.098039215686275</v>
       </c>
       <c r="H2">
-        <v>-0.7744119743406985</v>
+        <v>-2.098039215686275</v>
       </c>
       <c r="I2">
-        <v>-0.8321454027084818</v>
+        <v>-2.191176470588235</v>
       </c>
       <c r="J2">
-        <v>-0.8321454027084818</v>
+        <v>-2.191176470588235</v>
       </c>
       <c r="K2">
-        <v>-8.18</v>
+        <v>-1.674</v>
       </c>
       <c r="L2">
-        <v>-1.457590876692801</v>
+        <v>-0.8205882352941176</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,73 +630,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>3.35</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="V2">
-        <v>0.1395833333333333</v>
+        <v>0.06106194690265486</v>
       </c>
       <c r="W2">
-        <v>-0.3341450825825826</v>
+        <v>-0.1427074536140344</v>
       </c>
       <c r="X2">
-        <v>0.1007199718343139</v>
+        <v>0.08345159719452538</v>
       </c>
       <c r="Y2">
-        <v>-0.4348650544168965</v>
+        <v>-0.2261590508085597</v>
       </c>
       <c r="Z2">
-        <v>0.398862828713575</v>
+        <v>0.2045933206298265</v>
       </c>
       <c r="AA2">
-        <v>-0.3066115254531264</v>
+        <v>-0.4402256129605864</v>
       </c>
       <c r="AB2">
-        <v>0.09895410371556942</v>
+        <v>0.08114125569882205</v>
       </c>
       <c r="AC2">
-        <v>-0.4055656291686958</v>
+        <v>-0.5213668686594084</v>
       </c>
       <c r="AD2">
-        <v>0.6909999999999999</v>
+        <v>0.63</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0.6909999999999999</v>
+        <v>0.63</v>
       </c>
       <c r="AG2">
-        <v>-2.659</v>
+        <v>-0.05999999999999994</v>
       </c>
       <c r="AH2">
-        <v>0.02798590579563404</v>
+        <v>0.05280804694048617</v>
       </c>
       <c r="AI2">
-        <v>0.05389595195382575</v>
+        <v>0.05101214574898785</v>
       </c>
       <c r="AJ2">
-        <v>-0.1245958483669931</v>
+        <v>-0.005338078291814942</v>
       </c>
       <c r="AK2">
-        <v>-0.2807517685566466</v>
+        <v>-0.005145797598627783</v>
       </c>
       <c r="AL2">
-        <v>0.047</v>
+        <v>0.042</v>
       </c>
       <c r="AM2">
-        <v>0.043</v>
+        <v>0.029</v>
       </c>
       <c r="AN2">
-        <v>-0.1963068181818182</v>
+        <v>-0.1425339366515837</v>
       </c>
       <c r="AO2">
-        <v>-99.36170212765957</v>
+        <v>-106.4285714285714</v>
       </c>
       <c r="AP2">
-        <v>0.7553977272727272</v>
+        <v>0.01357466063348415</v>
       </c>
       <c r="AQ2">
-        <v>-108.6046511627907</v>
+        <v>-154.1379310344827</v>
       </c>
     </row>
     <row r="3">
@@ -715,23 +715,11 @@
           <t>Chemical (Specialty)</t>
         </is>
       </c>
-      <c r="G3">
-        <v>-412.9999999999999</v>
-      </c>
-      <c r="H3">
-        <v>-412.9999999999999</v>
-      </c>
-      <c r="I3">
-        <v>-545</v>
-      </c>
-      <c r="J3">
-        <v>-545</v>
+      <c r="D3">
+        <v>-0.722</v>
       </c>
       <c r="K3">
-        <v>-1.09</v>
-      </c>
-      <c r="L3">
-        <v>-545</v>
+        <v>-1.46</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -755,64 +743,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>1.07</v>
+        <v>0.184</v>
       </c>
       <c r="V3">
-        <v>0.08230769230769232</v>
+        <v>0.03511450381679389</v>
       </c>
       <c r="W3">
-        <v>-0.1892361111111111</v>
+        <v>-0.2543554006968641</v>
       </c>
       <c r="X3">
-        <v>0.09935064648703085</v>
+        <v>0.0821225796781862</v>
       </c>
       <c r="Y3">
-        <v>-0.288586757598142</v>
+        <v>-0.3364779803750503</v>
       </c>
       <c r="Z3">
-        <v>0.0003846153846153847</v>
+        <v>0</v>
       </c>
       <c r="AA3">
-        <v>-0.2096153846153846</v>
+        <v>-0.3126338329764454</v>
       </c>
       <c r="AB3">
-        <v>0.09935064648703085</v>
+        <v>0.08170246055446904</v>
       </c>
       <c r="AC3">
-        <v>-0.3089660311024155</v>
+        <v>-0.3943362935309144</v>
       </c>
       <c r="AD3">
-        <v>0</v>
+        <v>0.051</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>0</v>
+        <v>0.051</v>
       </c>
       <c r="AG3">
-        <v>-1.07</v>
+        <v>-0.133</v>
       </c>
       <c r="AH3">
-        <v>0</v>
+        <v>0.009639009639009637</v>
       </c>
       <c r="AI3">
-        <v>0</v>
+        <v>0.01019796040791842</v>
       </c>
       <c r="AJ3">
-        <v>-0.08968985750209557</v>
+        <v>-0.02604268650871353</v>
       </c>
       <c r="AK3">
-        <v>-0.2291220556745182</v>
+        <v>-0.02761054598297696</v>
       </c>
       <c r="AL3">
-        <v>0</v>
+        <v>0.003</v>
       </c>
       <c r="AM3">
-        <v>-0.001</v>
+        <v>-0.007</v>
+      </c>
+      <c r="AN3">
+        <v>-0.03493150684931506</v>
+      </c>
+      <c r="AO3">
+        <v>-486.6666666666666</v>
+      </c>
+      <c r="AP3">
+        <v>0.0910958904109589</v>
       </c>
       <c r="AQ3">
-        <v>1090</v>
+        <v>208.5714285714286</v>
       </c>
     </row>
     <row r="4">
@@ -832,25 +829,25 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.626</v>
+        <v>0.0655</v>
       </c>
       <c r="G4">
-        <v>-0.6270944741532977</v>
+        <v>-1.450980392156863</v>
       </c>
       <c r="H4">
-        <v>-0.6274509803921569</v>
+        <v>-1.450980392156863</v>
       </c>
       <c r="I4">
-        <v>-0.6381461675579322</v>
+        <v>-1.475490196078431</v>
       </c>
       <c r="J4">
-        <v>-0.6381461675579322</v>
+        <v>-1.475490196078431</v>
       </c>
       <c r="K4">
-        <v>-7.09</v>
+        <v>-0.214</v>
       </c>
       <c r="L4">
-        <v>-1.263814616755793</v>
+        <v>-0.1049019607843137</v>
       </c>
       <c r="M4">
         <v>-0</v>
@@ -874,73 +871,73 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>2.28</v>
+        <v>0.506</v>
       </c>
       <c r="V4">
-        <v>0.2072727272727272</v>
+        <v>0.0834983498349835</v>
       </c>
       <c r="W4">
-        <v>-0.479054054054054</v>
+        <v>-0.03105950653120465</v>
       </c>
       <c r="X4">
-        <v>0.102089297181597</v>
+        <v>0.08478061471086455</v>
       </c>
       <c r="Y4">
-        <v>-0.5811433512356511</v>
+        <v>-0.1158401212420692</v>
       </c>
       <c r="Z4">
-        <v>0.6324689966178129</v>
+        <v>0.3848330503678551</v>
       </c>
       <c r="AA4">
-        <v>-0.4036076662908681</v>
+        <v>-0.5678173929447273</v>
       </c>
       <c r="AB4">
-        <v>0.09855756094410802</v>
+        <v>0.08058005084317506</v>
       </c>
       <c r="AC4">
-        <v>-0.5021652272349761</v>
+        <v>-0.6483974437879024</v>
       </c>
       <c r="AD4">
-        <v>0.6909999999999999</v>
+        <v>0.579</v>
       </c>
       <c r="AE4">
         <v>0</v>
       </c>
       <c r="AF4">
-        <v>0.6909999999999999</v>
+        <v>0.579</v>
       </c>
       <c r="AG4">
-        <v>-1.589</v>
+        <v>0.07299999999999995</v>
       </c>
       <c r="AH4">
-        <v>0.05910529467111453</v>
+        <v>0.08721192950745595</v>
       </c>
       <c r="AI4">
-        <v>0.09758508685213953</v>
+        <v>0.07878622941896857</v>
       </c>
       <c r="AJ4">
-        <v>-0.1688449686537031</v>
+        <v>0.01190282080547855</v>
       </c>
       <c r="AK4">
-        <v>-0.3309727140179129</v>
+        <v>0.01066783574455647</v>
       </c>
       <c r="AL4">
-        <v>0.047</v>
+        <v>0.039</v>
       </c>
       <c r="AM4">
-        <v>0.044</v>
+        <v>0.036</v>
       </c>
       <c r="AN4">
-        <v>-0.1963068181818182</v>
+        <v>-0.1956081081081081</v>
       </c>
       <c r="AO4">
-        <v>-76.17021276595744</v>
+        <v>-77.17948717948717</v>
       </c>
       <c r="AP4">
-        <v>0.4514204545454545</v>
+        <v>-0.02466216216216215</v>
       </c>
       <c r="AQ4">
-        <v>-81.36363636363637</v>
+        <v>-83.61111111111111</v>
       </c>
     </row>
   </sheetData>
